--- a/tiflow/develop/2.0.0-ballot.1/ValueSet-tiflow-operation-outcome-details-vs.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/ValueSet-tiflow-operation-outcome-details-vs.xlsx
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/ValueSet/tiflow-operation-outcome-details-vs</t>
+    <t>https://gematik.de/fhir/tiflow/ValueSet/tiflow-operation-outcome-details-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -116,7 +116,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/CodeSystem/tiflow-operation-outcome-details-cs</t>
+    <t>https://gematik.de/fhir/tiflow/CodeSystem/tiflow-operation-outcome-details-cs</t>
   </si>
   <si>
     <t>Concept</t>
